--- a/PlanesEstudio/Plantilla_Plan_Prueba.xlsx
+++ b/PlanesEstudio/Plantilla_Plan_Prueba.xlsx
@@ -10,6 +10,7 @@
     <x:sheet name="Datos" sheetId="2" r:id="rId3"/>
     <x:sheet name="Optativas" sheetId="3" r:id="rId4"/>
     <x:sheet name="Instrucciones" sheetId="4" r:id="rId5"/>
+    <x:sheet name="Apoyos" sheetId="5" r:id="rId8"/>
   </x:sheets>
   <x:definedNames/>
   <x:calcPr calcId="125725"/>
@@ -199,7 +200,7 @@
     <x:t xml:space="preserve">  • Una fila por materia, empezando en la fila 2. No dejes filas vacías en medio: el sistema deja de leer en la primera fila sin nombre de materia.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">  • Semestre: número del periodo (1, 2, 3...).</x:t>
+    <x:t xml:space="preserve">  • Semestre: número del periodo (1, 2, 3...). En las AFEL déjalo vacío: no pertenecen a un periodo.</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">  • Materia: nombre completo.</x:t>
@@ -217,7 +218,7 @@
     <x:t xml:space="preserve">  • Area (opcional): General, Básica, Disciplinar o Terminal. Define el color de la tarjeta; vacía = gris.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">  • Las AFEL van en un número de semestre propio (el siguiente al último) para que salgan en la columna "Área Libre (AFEL)".</x:t>
+    <x:t xml:space="preserve">  • Las AFEL siempre salen juntas en la columna "Área Libre (AFEL)" al final del mapa, sin importar su semestre (déjalo vacío). El plan puede tener los semestres que necesite.</x:t>
   </x:si>
   <x:si>
     <x:t>HOJA "Datos" (opcional)</x:t>
@@ -242,6 +243,51 @@
   </x:si>
   <x:si>
     <x:t>No cambies el orden de las columnas ni los nombres de las hojas "Datos" y "Optativas".</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Periodos trayectoria larga</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Plazo máximo en periodos (ritmo mínimo). Si se deja vacío se usa 1.5 veces la duración del plan (9).</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Apoyo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Horario, lugar o cómo solicitarlo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Asesorías académicas (PAFI)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Escribir aquí el horario y lugar (consultar con la coordinación de tutorías)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Asesoría de pares</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Escribir aquí el horario y lugar</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CENDHIU (apoyo psicológico)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Con cita, a través de la coordinación de tutorías</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Becas y apoyos económicos</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Convocatorias vigentes en la secretaría de la facultad</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Centro de Idiomas / Autoacceso</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">  • Hoja Datos, "Periodos trayectoria larga": el plazo máximo en periodos. Sirve para avisar cuando el alumno va debajo del mínimo de créditos. Si se deja vacío se usa 1.5 veces la duración del plan.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">  • Hoja Apoyos (opcional): los apoyos de la facultad con su horario y lugar. Se imprimen en la ficha que el tutor lleva a la sesión.</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -251,7 +297,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="0" formatCode=""/>
   </x:numFmts>
-  <x:fonts count="3">
+  <x:fonts count="4">
     <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="11"/>
@@ -272,6 +318,14 @@
       <x:vertAlign val="baseline"/>
       <x:sz val="14"/>
       <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:i/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="11"/>
+      <x:color rgb="FF808080"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
@@ -308,7 +362,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="4">
+  <x:cellStyleXfs count="5">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -321,8 +375,11 @@
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="4">
+  <x:cellXfs count="5">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -336,6 +393,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1206,9 +1267,6 @@
       </x:c>
     </x:row>
     <x:row r="29" spans="1:6">
-      <x:c r="A29" s="0">
-        <x:v>7</x:v>
-      </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>41</x:v>
       </x:c>
@@ -1226,9 +1284,6 @@
       </x:c>
     </x:row>
     <x:row r="30" spans="1:6">
-      <x:c r="A30" s="0">
-        <x:v>7</x:v>
-      </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>43</x:v>
       </x:c>
@@ -1272,11 +1327,12 @@
   <x:dimension ref="A1:B2"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="14.996339" style="2" customWidth="1"/>
+    <x:col min="1" max="1" width="23.996339" style="2" customWidth="1"/>
     <x:col min="2" max="2" width="43.710625" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="89.282054" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:2">
+    <x:row r="1" spans="1:3">
       <x:c r="A1" s="2" t="s">
         <x:v>44</x:v>
       </x:c>
@@ -1284,12 +1340,23 @@
         <x:v>45</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:2">
+    <x:row r="2" spans="1:3">
       <x:c r="A2" s="2" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="B2" s="0">
         <x:v>216</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:3">
+      <x:c r="A3" s="2" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B3" s="0">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C3" s="4" t="s">
+        <x:v>76</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1499,6 +1566,85 @@
         <x:v>74</x:v>
       </x:c>
     </x:row>
+    <x:row r="24" spans="1:1">
+      <x:c r="A24" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:1">
+      <x:c r="A25" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter/>
+  <x:tableParts count="0"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:B6"/>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="29.710625" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="65.710625" style="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:2">
+      <x:c r="A1" s="1" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B1" s="1" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:2">
+      <x:c r="A2" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:2">
+      <x:c r="A3" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:2">
+      <x:c r="A4" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:2">
+      <x:c r="A5" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:2">
+      <x:c r="A6" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/PlanesEstudio/Plantilla_Plan_Prueba.xlsx
+++ b/PlanesEstudio/Plantilla_Plan_Prueba.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.282054" customWidth="1" style="5" min="1" max="1"/>
@@ -496,6 +496,7 @@
     <col width="34.424911" customWidth="1" style="5" min="5" max="5"/>
     <col width="9.996339000000001" customWidth="1" style="5" min="6" max="6"/>
     <col width="20" customWidth="1" style="6" min="7" max="7"/>
+    <col width="18" customWidth="1" style="6" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="7">
@@ -534,6 +535,11 @@
           <t>Creditos minimos (%)</t>
         </is>
       </c>
+      <c r="H1" s="7" t="inlineStr">
+        <is>
+          <t>Periodos que dura</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="n">
@@ -559,6 +565,7 @@
         </is>
       </c>
       <c r="G2" s="5" t="n"/>
+      <c r="H2" s="5" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
@@ -584,6 +591,7 @@
         </is>
       </c>
       <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
@@ -609,6 +617,7 @@
         </is>
       </c>
       <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
@@ -634,6 +643,7 @@
         </is>
       </c>
       <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
@@ -659,6 +669,7 @@
         </is>
       </c>
       <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
@@ -688,6 +699,7 @@
         </is>
       </c>
       <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
@@ -717,6 +729,7 @@
         </is>
       </c>
       <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
@@ -746,6 +759,7 @@
         </is>
       </c>
       <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
@@ -775,6 +789,7 @@
         </is>
       </c>
       <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
@@ -800,6 +815,7 @@
         </is>
       </c>
       <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
@@ -825,6 +841,7 @@
         </is>
       </c>
       <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
@@ -854,6 +871,7 @@
         </is>
       </c>
       <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
@@ -883,6 +901,7 @@
         </is>
       </c>
       <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
@@ -908,6 +927,7 @@
         </is>
       </c>
       <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
@@ -929,6 +949,7 @@
       <c r="E16" s="5" t="inlineStr"/>
       <c r="F16" s="5" t="inlineStr"/>
       <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
@@ -958,6 +979,7 @@
         </is>
       </c>
       <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
@@ -987,6 +1009,7 @@
         </is>
       </c>
       <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
@@ -1016,6 +1039,7 @@
         </is>
       </c>
       <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
@@ -1045,6 +1069,7 @@
         </is>
       </c>
       <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
@@ -1074,6 +1099,7 @@
         </is>
       </c>
       <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
@@ -1103,6 +1129,7 @@
         </is>
       </c>
       <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
@@ -1128,6 +1155,7 @@
         </is>
       </c>
       <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
@@ -1149,6 +1177,7 @@
       <c r="E24" s="5" t="inlineStr"/>
       <c r="F24" s="5" t="inlineStr"/>
       <c r="G24" s="5" t="n"/>
+      <c r="H24" s="5" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
@@ -1178,6 +1207,7 @@
         </is>
       </c>
       <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
@@ -1205,6 +1235,9 @@
       <c r="G26" s="5" t="n">
         <v>70</v>
       </c>
+      <c r="H26" s="5" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
@@ -1232,6 +1265,7 @@
       <c r="G27" s="5" t="n">
         <v>70</v>
       </c>
+      <c r="H27" s="5" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
@@ -1263,6 +1297,7 @@
       <c r="G28" s="5" t="n">
         <v>70</v>
       </c>
+      <c r="H28" s="5" t="n"/>
     </row>
     <row r="29">
       <c r="B29" s="5" t="inlineStr">
@@ -1281,6 +1316,7 @@
       <c r="E29" s="5" t="inlineStr"/>
       <c r="F29" s="5" t="inlineStr"/>
       <c r="G29" s="5" t="n"/>
+      <c r="H29" s="5" t="n"/>
     </row>
     <row r="30">
       <c r="B30" s="5" t="inlineStr">
@@ -1299,6 +1335,7 @@
       <c r="E30" s="5" t="inlineStr"/>
       <c r="F30" s="5" t="inlineStr"/>
       <c r="G30" s="5" t="n"/>
+      <c r="H30" s="5" t="n"/>
     </row>
     <row r="31"/>
   </sheetData>
@@ -1484,7 +1521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A26"/>
+  <dimension ref="A1:A27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150.710625" customWidth="1" style="5" min="1" max="1"/>
@@ -1566,85 +1603,92 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">  • Periodos que dura (opcional): cuántos periodos puede durar la materia. Se usa 2 en Servicio social; vacía = 1. Mientras siga "cursando" dentro de ese plazo, en el periodo siguiente no se cuenta como rezago.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">  • Las AFEL siempre salen juntas en la columna "Área Libre (AFEL)" al final del mapa, sin importar su semestre (déjalo vacío). El plan puede tener los semestres que necesite.</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr"/>
-    </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>HOJA "Datos" (opcional)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • Programa: nombre que aparece en el título del mapa y en el Word de tutorías. Si falta, se usa el nombre del archivo.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">  • Programa: nombre que aparece en el título del mapa y en el Word de tutorías. Si falta, se usa el nombre del archivo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">  • Creditos totales: total oficial del plan, contra el que se calcula el % de avance. Si falta, se suman los créditos de la hoja Materias.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr"/>
-    </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>HOJA "Optativas" (opcional)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • Columna A: nombre de cada optativa que el alumno puede elegir. Columna B (opcional): grupo o área para ordenarlas.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">  • Columna A: nombre de cada optativa que el alumno puede elegir. Columna B (opcional): grupo o área para ordenarlas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">  • Si falta, las tarjetas de optativa conservan su nombre ("Optativa 1") y se pueden marcar igual.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr"/>
-    </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>PARA SUBIRLA: guarda el archivo con el nombre del plan (ej. Plan_Administracion_2020.xlsx) y súbelo en el sistema con el botón "Planes".</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>No cambies el orden de las columnas ni los nombres de las hojas "Datos" y "Optativas".</t>
         </is>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • Hoja Datos, "Periodos trayectoria larga": el plazo máximo en periodos. Sirve para avisar cuando el alumno va debajo del mínimo de créditos. Si se deja vacío se usa 1.5 veces la duración del plan.</t>
-        </is>
-      </c>
-    </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Hoja Datos, "Periodos trayectoria larga": el plazo máximo en periodos. Sirve para avisar cuando el alumno va debajo del mínimo de créditos. Si se deja vacío se usa 1.5 veces la duración del plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  • Hoja Apoyos (opcional): los apoyos de la facultad con su horario y lugar. Se imprimen en la ficha que el tutor lleva a la sesión.</t>
         </is>

--- a/PlanesEstudio/Plantilla_Plan_Prueba.xlsx
+++ b/PlanesEstudio/Plantilla_Plan_Prueba.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.282054" customWidth="1" style="5" min="1" max="1"/>
@@ -494,7 +494,7 @@
     <col width="8.424911" customWidth="1" style="5" min="3" max="3"/>
     <col width="8.710625" customWidth="1" style="5" min="4" max="4"/>
     <col width="34.424911" customWidth="1" style="5" min="5" max="5"/>
-    <col width="9.996339000000001" customWidth="1" style="5" min="6" max="6"/>
+    <col width="26" customWidth="1" style="5" min="6" max="6"/>
     <col width="20" customWidth="1" style="6" min="7" max="7"/>
     <col width="18" customWidth="1" style="6" min="8" max="8"/>
   </cols>
@@ -561,7 +561,7 @@
       <c r="E2" s="5" t="inlineStr"/>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Iniciación a la disciplina</t>
         </is>
       </c>
       <c r="G2" s="5" t="n"/>
@@ -587,7 +587,7 @@
       <c r="E3" s="5" t="inlineStr"/>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Iniciación a la disciplina</t>
         </is>
       </c>
       <c r="G3" s="5" t="n"/>
@@ -613,7 +613,7 @@
       <c r="E4" s="5" t="inlineStr"/>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Iniciación a la disciplina</t>
         </is>
       </c>
       <c r="G4" s="5" t="n"/>
@@ -639,7 +639,7 @@
       <c r="E5" s="5" t="inlineStr"/>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>AFBG</t>
         </is>
       </c>
       <c r="G5" s="5" t="n"/>
@@ -665,7 +665,7 @@
       <c r="E6" s="5" t="inlineStr"/>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>AFBG</t>
         </is>
       </c>
       <c r="G6" s="5" t="n"/>
@@ -695,7 +695,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Iniciación a la disciplina</t>
         </is>
       </c>
       <c r="G7" s="5" t="n"/>
@@ -725,7 +725,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Iniciación a la disciplina</t>
         </is>
       </c>
       <c r="G8" s="5" t="n"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Iniciación a la disciplina</t>
         </is>
       </c>
       <c r="G9" s="5" t="n"/>
@@ -785,7 +785,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>AFBG</t>
         </is>
       </c>
       <c r="G10" s="5" t="n"/>
@@ -811,7 +811,7 @@
       <c r="E11" s="5" t="inlineStr"/>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>AFBG</t>
         </is>
       </c>
       <c r="G11" s="5" t="n"/>
@@ -1337,14 +1337,13 @@
       <c r="G30" s="5" t="n"/>
       <c r="H30" s="5" t="n"/>
     </row>
-    <row r="31"/>
   </sheetData>
   <dataValidations count="2">
     <dataValidation sqref="D2:D200" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="" error="" promptTitle="" prompt="" type="list" errorStyle="stop" operator="between">
       <formula1>"Normal,Optativa,AFEL"</formula1>
     </dataValidation>
     <dataValidation sqref="F2:F200" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="" error="" promptTitle="" prompt="" type="list" errorStyle="stop" operator="between">
-      <formula1>"General,Básica,Disciplinar,Terminal"</formula1>
+      <formula1>"AFBG,Iniciación a la disciplina,Disciplinar,Terminal"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
@@ -1589,7 +1588,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Area (opcional): General, Básica, Disciplinar o Terminal. Define el color de la tarjeta; vacía = gris.</t>
+          <t xml:space="preserve">  • Area (opcional): AFBG, Iniciación a la disciplina, Disciplinar o Terminal. Define el color de la tarjeta; vacía = gris.</t>
         </is>
       </c>
     </row>
